--- a/apps/web/public/descargas/plantilla-matriz-iperc.xlsx
+++ b/apps/web/public/descargas/plantilla-matriz-iperc.xlsx
@@ -1,59 +1,280 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="IPERC" sheetId="1" r:id="rId1"/>
-    <sheet name="Guía" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="IPERC" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Guía" state="visible" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+  <si>
+    <t>MATRIZ IPERC — Identificación de Peligros, Evaluación de Riesgos y Controles</t>
+  </si>
+  <si>
+    <t>Empresa:</t>
+  </si>
+  <si>
+    <t>Área / Proceso:</t>
+  </si>
+  <si>
+    <t>Fecha:</t>
+  </si>
+  <si>
+    <t>Responsable:</t>
+  </si>
+  <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>Proceso / Tarea</t>
+  </si>
+  <si>
+    <t>Peligro identificado</t>
+  </si>
+  <si>
+    <t>Tipo de peligro</t>
+  </si>
+  <si>
+    <t>Personas expuestas</t>
+  </si>
+  <si>
+    <t>Probabilidad (1-5)</t>
+  </si>
+  <si>
+    <t>Impacto / Severidad (1-5)</t>
+  </si>
+  <si>
+    <t>Nivel de riesgo (P×I)</t>
+  </si>
+  <si>
+    <t>Evaluación del riesgo</t>
+  </si>
+  <si>
+    <t>Controles existentes</t>
+  </si>
+  <si>
+    <t>¿Suficiente? (S/N)</t>
+  </si>
+  <si>
+    <t>Plan de acción</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Fecha límite</t>
+  </si>
+  <si>
+    <t>Prob. post</t>
+  </si>
+  <si>
+    <t>Imp. post</t>
+  </si>
+  <si>
+    <t>Nivel residual</t>
+  </si>
+  <si>
+    <t>Carga y descarga de mercadería</t>
+  </si>
+  <si>
+    <t>Golpe por autoelevador</t>
+  </si>
+  <si>
+    <t>Mecánico</t>
+  </si>
+  <si>
+    <t>Operarios de depósito</t>
+  </si>
+  <si>
+    <t>ALTO</t>
+  </si>
+  <si>
+    <t>Delimitación de zonas peatonales, chaleco reflectivo</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Instalar barreras físicas y semáforo de cruce</t>
+  </si>
+  <si>
+    <t>Resp. SSOMA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mantenimiento eléctrico</t>
+  </si>
+  <si>
+    <t>Contacto con partes energizadas</t>
+  </si>
+  <si>
+    <t>Eléctrico</t>
+  </si>
+  <si>
+    <t>Técnicos de mantenimiento</t>
+  </si>
+  <si>
+    <t>Bloqueo y etiquetado (LOTO), guantes dieléctricos</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Resp. Mantenimiento</t>
+  </si>
+  <si>
+    <t>Trabajo administrativo en oficina</t>
+  </si>
+  <si>
+    <t>Trastorno musculoesquelético</t>
+  </si>
+  <si>
+    <t>Ergonómico</t>
+  </si>
+  <si>
+    <t>Personal administrativo</t>
+  </si>
+  <si>
+    <t>MODERADO</t>
+  </si>
+  <si>
+    <t>Pausas activas cada 2 horas</t>
+  </si>
+  <si>
+    <t>Evaluación ergonómica de puestos de trabajo</t>
+  </si>
+  <si>
+    <t>Resp. RRHH</t>
+  </si>
+  <si>
+    <t>Escala: 1-4 BAJO (aceptable) · 5-9 MODERADO (controlar) · 10-14 ALTO (acción requerida) · 15-25 CRÍTICO (acción inmediata)</t>
+  </si>
+  <si>
+    <t>Las filas 5-7 son ejemplos — borralas y cargá tu matriz. El nivel de riesgo y la evaluación se calculan automáticamente.</t>
+  </si>
+  <si>
+    <t>CÓMO USAR LA MATRIZ IPERC</t>
+  </si>
+  <si>
+    <t>1. Listá los procesos o tareas del área a evaluar (columna B).</t>
+  </si>
+  <si>
+    <t>2. Para cada tarea identificá los peligros (mecánico, eléctrico, ergonómico, químico, biológico, físico, psicosocial).</t>
+  </si>
+  <si>
+    <t>3. Evaluá probabilidad (1 = raro … 5 = casi seguro) e impacto (1 = leve … 5 = catastrófico).</t>
+  </si>
+  <si>
+    <t>4. El nivel de riesgo (P×I) y la evaluación se calculan automáticamente.</t>
+  </si>
+  <si>
+    <t>5. Priorizá acciones en riesgos ALTOS y CRÍTICOS; documentá controles existentes.</t>
+  </si>
+  <si>
+    <t>6. Si el control no es suficiente, definí plan de acción con responsable y fecha límite.</t>
+  </si>
+  <si>
+    <t>7. Re-evaluá después de implementar el control (columnas post-control) — esa es la evidencia de eficacia para el auditor.</t>
+  </si>
+  <si>
+    <t>TIP: en SGI360 esta matriz vive dentro del sistema con responsables, alertas de vencimiento y trazabilidad completa → logismart.ar</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF94A3B8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF166534"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF166534"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDBA74"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86EFAC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE047"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -61,18 +282,89 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF166534"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,305 +689,731 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="78.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>MATRIZ IPERC — Identificación de Peligros, Evaluación de Riesgos y Controles</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Empresa:</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>Área/Proceso:</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>Fecha:</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>Responsable:</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>N°</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Proceso/Tarea</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Peligro identificado</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Tipo de peligro</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Personas expuestas</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Probabilidad (1-5)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Impacto/Severidad (1-5)</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Nivel de riesgo (PxI)</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Controles existentes</v>
-      </c>
-      <c r="J4" t="str">
-        <v>¿Control suficiente? (S/N)</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Plan de acción</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Responsable</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Fecha límite</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Prob. post-control</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Imp. post-control</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Nivel residual</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
+    <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="str">
-        <v>Ej: Carga y descarga de mercadería</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Golpe por autoelevador</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Mecánico</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Operarios de depósito</v>
-      </c>
-      <c r="F5">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H5" t="str">
-        <v>=F5*G5</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Delimitación de zonas peatonales, chaleco reflectivo</v>
-      </c>
-      <c r="J5" t="str">
-        <v>N</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Instalar barreras físicas y semáforo de cruce</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Resp. SSOMA</v>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="34" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="O5">
+      <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6">
         <v>4</v>
       </c>
-      <c r="P5" t="str">
-        <v>=M5*N5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
+      <c r="H5" s="7">
+        <f>F5*G5</f>
+        <v>12</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="6">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="8">
+        <f>O5*P5</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
         <v>2</v>
       </c>
-      <c r="B6" t="str">
-        <v>Ej: Mantenimiento eléctrico</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Contacto con partes energizadas</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Eléctrico</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Técnicos</v>
-      </c>
-      <c r="F6">
+      <c r="B6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="9">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="9">
         <v>5</v>
       </c>
-      <c r="H6" t="str">
-        <v>=F6*G6</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Bloqueo y etiquetado (LOTO)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>S</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>Resp. Mantenimiento</v>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6">
+      <c r="H6" s="7">
+        <f>F6*G6</f>
+        <v>10</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" s="9">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="P6" s="9">
         <v>5</v>
       </c>
-      <c r="P6" t="str">
-        <v>=M6*N6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
+      <c r="Q6" s="10">
+        <f>O6*P6</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" t="str">
-        <v>Ej: Trabajo en mostrador</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Trastorno musculoesquelético</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Ergonómico</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Personal administrativo</v>
-      </c>
-      <c r="F7">
+      <c r="B7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="6">
         <v>4</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="6">
         <v>2</v>
       </c>
-      <c r="H7" t="str">
-        <v>=F7*G7</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Pausas activas cada 2h</v>
-      </c>
-      <c r="J7" t="str">
-        <v>N</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Evaluación ergonómica de puestos</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Resp. RRHH</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7">
+      <c r="H7" s="10">
+        <f>F7*G7</f>
+        <v>8</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" s="6">
         <v>2</v>
       </c>
-      <c r="O7">
+      <c r="P7" s="6">
         <v>2</v>
       </c>
-      <c r="P7" t="str">
-        <v>=M7*N7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Escala de nivel de riesgo:  1-4 Bajo (aceptable) · 5-9 Moderado (controlar) · 10-14 Alto (acción requerida) · 15-25 Crítico (acción inmediata)</v>
-      </c>
+      <c r="Q7" s="8">
+        <f>O7*P7</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6">
+        <f>IF(AND(F8&lt;&gt;"",G8&lt;&gt;""),F8*G8,"")</f>
+      </c>
+      <c r="I8" s="6">
+        <f>IF(H8="","",IF(H8&gt;=15,"CRÍTICO",IF(H8&gt;=10,"ALTO",IF(H8&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6">
+        <f>IF(AND(O8&lt;&gt;"",P8&lt;&gt;""),O8*P8,"")</f>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <f>IF(AND(F9&lt;&gt;"",G9&lt;&gt;""),F9*G9,"")</f>
+      </c>
+      <c r="I9" s="6">
+        <f>IF(H9="","",IF(H9&gt;=15,"CRÍTICO",IF(H9&gt;=10,"ALTO",IF(H9&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6">
+        <f>IF(AND(O9&lt;&gt;"",P9&lt;&gt;""),O9*P9,"")</f>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
+        <f>IF(AND(F10&lt;&gt;"",G10&lt;&gt;""),F10*G10,"")</f>
+      </c>
+      <c r="I10" s="6">
+        <f>IF(H10="","",IF(H10&gt;=15,"CRÍTICO",IF(H10&gt;=10,"ALTO",IF(H10&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6">
+        <f>IF(AND(O10&lt;&gt;"",P10&lt;&gt;""),O10*P10,"")</f>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
+        <f>IF(AND(F11&lt;&gt;"",G11&lt;&gt;""),F11*G11,"")</f>
+      </c>
+      <c r="I11" s="6">
+        <f>IF(H11="","",IF(H11&gt;=15,"CRÍTICO",IF(H11&gt;=10,"ALTO",IF(H11&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6">
+        <f>IF(AND(O11&lt;&gt;"",P11&lt;&gt;""),O11*P11,"")</f>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <f>IF(AND(F12&lt;&gt;"",G12&lt;&gt;""),F12*G12,"")</f>
+      </c>
+      <c r="I12" s="6">
+        <f>IF(H12="","",IF(H12&gt;=15,"CRÍTICO",IF(H12&gt;=10,"ALTO",IF(H12&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6">
+        <f>IF(AND(O12&lt;&gt;"",P12&lt;&gt;""),O12*P12,"")</f>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <f>IF(AND(F13&lt;&gt;"",G13&lt;&gt;""),F13*G13,"")</f>
+      </c>
+      <c r="I13" s="6">
+        <f>IF(H13="","",IF(H13&gt;=15,"CRÍTICO",IF(H13&gt;=10,"ALTO",IF(H13&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6">
+        <f>IF(AND(O13&lt;&gt;"",P13&lt;&gt;""),O13*P13,"")</f>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
+        <f>IF(AND(F14&lt;&gt;"",G14&lt;&gt;""),F14*G14,"")</f>
+      </c>
+      <c r="I14" s="6">
+        <f>IF(H14="","",IF(H14&gt;=15,"CRÍTICO",IF(H14&gt;=10,"ALTO",IF(H14&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6">
+        <f>IF(AND(O14&lt;&gt;"",P14&lt;&gt;""),O14*P14,"")</f>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6">
+        <f>IF(AND(F15&lt;&gt;"",G15&lt;&gt;""),F15*G15,"")</f>
+      </c>
+      <c r="I15" s="6">
+        <f>IF(H15="","",IF(H15&gt;=15,"CRÍTICO",IF(H15&gt;=10,"ALTO",IF(H15&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6">
+        <f>IF(AND(O15&lt;&gt;"",P15&lt;&gt;""),O15*P15,"")</f>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
+        <f>IF(AND(F16&lt;&gt;"",G16&lt;&gt;""),F16*G16,"")</f>
+      </c>
+      <c r="I16" s="6">
+        <f>IF(H16="","",IF(H16&gt;=15,"CRÍTICO",IF(H16&gt;=10,"ALTO",IF(H16&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6">
+        <f>IF(AND(O16&lt;&gt;"",P16&lt;&gt;""),O16*P16,"")</f>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6">
+        <f>IF(AND(F17&lt;&gt;"",G17&lt;&gt;""),F17*G17,"")</f>
+      </c>
+      <c r="I17" s="6">
+        <f>IF(H17="","",IF(H17&gt;=15,"CRÍTICO",IF(H17&gt;=10,"ALTO",IF(H17&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6">
+        <f>IF(AND(O17&lt;&gt;"",P17&lt;&gt;""),O17*P17,"")</f>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6">
+        <f>IF(AND(F18&lt;&gt;"",G18&lt;&gt;""),F18*G18,"")</f>
+      </c>
+      <c r="I18" s="6">
+        <f>IF(H18="","",IF(H18&gt;=15,"CRÍTICO",IF(H18&gt;=10,"ALTO",IF(H18&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6">
+        <f>IF(AND(O18&lt;&gt;"",P18&lt;&gt;""),O18*P18,"")</f>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6">
+        <f>IF(AND(F19&lt;&gt;"",G19&lt;&gt;""),F19*G19,"")</f>
+      </c>
+      <c r="I19" s="6">
+        <f>IF(H19="","",IF(H19&gt;=15,"CRÍTICO",IF(H19&gt;=10,"ALTO",IF(H19&gt;=5,"MODERADO","BAJO"))))</f>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6">
+        <f>IF(AND(O19&lt;&gt;"",P19&lt;&gt;""),O19*P19,"")</f>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P9"/>
-  </ignoredErrors>
+  <mergeCells count="3">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="A22:Q22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="60.83203125" customWidth="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>CÓMO USAR LA PLANTILLA</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1. Listá los procesos o tareas del área a evaluar.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2. Para cada tarea identificá los peligros (mecánico, eléctrico, ergonómico, químico, biológico, físico, psicosocial).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>3. Evaluá probabilidad (1=raro … 5=casi seguro) e impacto (1=leve … 5=catastrófico).</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>4. Nivel = P×I se calcula solo. Priorizá acciones en riesgos Altos y Críticos.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>5. Documentá controles existentes; si no son suficientes, definí plan de acción con responsable y fecha.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>6. Re-evaluá después de implementar el control (columnas post-control) — es la evidencia de eficacia.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>TIP: en SGI360 esta matriz vive dentro del sistema con responsables, alertas y trazabilidad → logismart.ar</v>
+    <row r="1" ht="28" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>